--- a/artfynd/A 60503-2023 artfynd.xlsx
+++ b/artfynd/A 60503-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60503-2023 artfynd.xlsx
+++ b/artfynd/A 60503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4311,6 +4311,113 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122507139</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57379</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Myrsnipmyrarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>509228</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7107904</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60503-2023 artfynd.xlsx
+++ b/artfynd/A 60503-2023 artfynd.xlsx
@@ -4331,11 +4331,6 @@
       <c r="E36" t="n">
         <v>100109</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 60503-2023 artfynd.xlsx
+++ b/artfynd/A 60503-2023 artfynd.xlsx
@@ -4316,7 +4316,7 @@
         <v>122507139</v>
       </c>
       <c r="B36" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4330,6 +4330,11 @@
       </c>
       <c r="E36" t="n">
         <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>

--- a/artfynd/A 60503-2023 artfynd.xlsx
+++ b/artfynd/A 60503-2023 artfynd.xlsx
@@ -4316,7 +4316,7 @@
         <v>122507139</v>
       </c>
       <c r="B36" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 60503-2023 artfynd.xlsx
+++ b/artfynd/A 60503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113557445</v>
+        <v>113557466</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509231</v>
+        <v>509318</v>
       </c>
       <c r="R2" t="n">
-        <v>7107892</v>
+        <v>7107630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113557455</v>
+        <v>113557422</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509281</v>
+        <v>509446</v>
       </c>
       <c r="R3" t="n">
-        <v>7107661</v>
+        <v>7107561</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,12 +882,7 @@
         <v>113557423</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113557440</v>
+        <v>113557424</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509120</v>
+        <v>509396</v>
       </c>
       <c r="R5" t="n">
-        <v>7107842</v>
+        <v>7107636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113557457</v>
+        <v>113557425</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509336</v>
+        <v>509393</v>
       </c>
       <c r="R6" t="n">
-        <v>7107570</v>
+        <v>7107635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113557429</v>
+        <v>113557426</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509297</v>
+        <v>509357</v>
       </c>
       <c r="R7" t="n">
-        <v>7107765</v>
+        <v>7107615</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113557428</v>
+        <v>113557427</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509307</v>
+        <v>509308</v>
       </c>
       <c r="R8" t="n">
-        <v>7107759</v>
+        <v>7107764</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack 2 träd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113557425</v>
+        <v>113557428</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509393</v>
+        <v>509307</v>
       </c>
       <c r="R9" t="n">
-        <v>7107635</v>
+        <v>7107759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113557446</v>
+        <v>113557429</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509235</v>
+        <v>509297</v>
       </c>
       <c r="R10" t="n">
-        <v>7107837</v>
+        <v>7107765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Obs</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113557422</v>
+        <v>113557430</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509446</v>
+        <v>509275</v>
       </c>
       <c r="R11" t="n">
-        <v>7107561</v>
+        <v>7107751</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113557437</v>
+        <v>113557431</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509198</v>
+        <v>509224</v>
       </c>
       <c r="R12" t="n">
-        <v>7107921</v>
+        <v>7107780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113557456</v>
+        <v>113557432</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509346</v>
+        <v>509277</v>
       </c>
       <c r="R13" t="n">
-        <v>7107579</v>
+        <v>7107822</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1872,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113557447</v>
+        <v>113557433</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509206</v>
+        <v>509272</v>
       </c>
       <c r="R14" t="n">
-        <v>7107821</v>
+        <v>7107846</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,15 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113557438</v>
+        <v>113557434</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509161</v>
+        <v>509234</v>
       </c>
       <c r="R15" t="n">
-        <v>7107926</v>
+        <v>7107901</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,15 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113557454</v>
+        <v>113557435</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509275</v>
+        <v>509216</v>
       </c>
       <c r="R16" t="n">
-        <v>7107665</v>
+        <v>7107909</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113557451</v>
+        <v>113557436</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509157</v>
+        <v>509209</v>
       </c>
       <c r="R17" t="n">
-        <v>7107768</v>
+        <v>7107928</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,15 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113557431</v>
+        <v>113557437</v>
       </c>
       <c r="B18" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509224</v>
+        <v>509198</v>
       </c>
       <c r="R18" t="n">
-        <v>7107780</v>
+        <v>7107921</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,15 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113557449</v>
+        <v>113557438</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509196</v>
+        <v>509161</v>
       </c>
       <c r="R19" t="n">
-        <v>7107796</v>
+        <v>7107926</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,15 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113557426</v>
+        <v>113557439</v>
       </c>
       <c r="B20" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509357</v>
+        <v>509155</v>
       </c>
       <c r="R20" t="n">
-        <v>7107615</v>
+        <v>7107889</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,15 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113557427</v>
+        <v>113557440</v>
       </c>
       <c r="B21" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509308</v>
+        <v>509120</v>
       </c>
       <c r="R21" t="n">
-        <v>7107764</v>
+        <v>7107842</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack 2 träd</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,15 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113557450</v>
+        <v>113557441</v>
       </c>
       <c r="B22" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509190</v>
+        <v>509133</v>
       </c>
       <c r="R22" t="n">
-        <v>7107793</v>
+        <v>7107860</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,15 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113557444</v>
+        <v>113557442</v>
       </c>
       <c r="B23" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509204</v>
+        <v>509180</v>
       </c>
       <c r="R23" t="n">
-        <v>7107904</v>
+        <v>7107902</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,15 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113557439</v>
+        <v>113557444</v>
       </c>
       <c r="B24" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509155</v>
+        <v>509204</v>
       </c>
       <c r="R24" t="n">
-        <v>7107889</v>
+        <v>7107904</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,15 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113557448</v>
+        <v>113557445</v>
       </c>
       <c r="B25" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3176,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509198</v>
+        <v>509231</v>
       </c>
       <c r="R25" t="n">
-        <v>7107812</v>
+        <v>7107892</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,15 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113557441</v>
+        <v>113557446</v>
       </c>
       <c r="B26" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509133</v>
+        <v>509235</v>
       </c>
       <c r="R26" t="n">
-        <v>7107860</v>
+        <v>7107837</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,15 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113557424</v>
+        <v>113557447</v>
       </c>
       <c r="B27" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3390,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509396</v>
+        <v>509206</v>
       </c>
       <c r="R27" t="n">
-        <v>7107636</v>
+        <v>7107821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3300,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,15 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113557435</v>
+        <v>113557448</v>
       </c>
       <c r="B28" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509216</v>
+        <v>509198</v>
       </c>
       <c r="R28" t="n">
-        <v>7107909</v>
+        <v>7107812</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,15 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113557436</v>
+        <v>113557449</v>
       </c>
       <c r="B29" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509209</v>
+        <v>509196</v>
       </c>
       <c r="R29" t="n">
-        <v>7107928</v>
+        <v>7107796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3671,15 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113557433</v>
+        <v>113557450</v>
       </c>
       <c r="B30" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,10 +3566,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509272</v>
+        <v>509190</v>
       </c>
       <c r="R30" t="n">
-        <v>7107846</v>
+        <v>7107793</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,15 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113557442</v>
+        <v>113557451</v>
       </c>
       <c r="B31" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3818,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509180</v>
+        <v>509157</v>
       </c>
       <c r="R31" t="n">
-        <v>7107902</v>
+        <v>7107768</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3885,15 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113557430</v>
+        <v>113557453</v>
       </c>
       <c r="B32" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3925,10 +3770,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509275</v>
+        <v>509194</v>
       </c>
       <c r="R32" t="n">
-        <v>7107751</v>
+        <v>7107716</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3992,15 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113557434</v>
+        <v>113557454</v>
       </c>
       <c r="B33" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,10 +3872,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509234</v>
+        <v>509275</v>
       </c>
       <c r="R33" t="n">
-        <v>7107901</v>
+        <v>7107665</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4072,7 +3912,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,15 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113557432</v>
+        <v>113557455</v>
       </c>
       <c r="B34" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4139,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509277</v>
+        <v>509281</v>
       </c>
       <c r="R34" t="n">
-        <v>7107822</v>
+        <v>7107661</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,15 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113557466</v>
+        <v>113557456</v>
       </c>
       <c r="B35" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4222,21 +4052,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4246,10 +4076,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509318</v>
+        <v>509346</v>
       </c>
       <c r="R35" t="n">
-        <v>7107630</v>
+        <v>7107579</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,7 +4116,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,15 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122507139</v>
+        <v>113557457</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4349,14 +4174,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Myrsnipmyrarna, Jmt</t>
+          <t>Åslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509228</v>
+        <v>509336</v>
       </c>
       <c r="R36" t="n">
-        <v>7107904</v>
+        <v>7107570</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,17 +4208,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4417,6 +4242,618 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>113557458</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Åslåttjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>509294</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7107582</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122507135</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Myrsnipmyrarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>509339</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7107799</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122507136</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Myrsnipmyrarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>509333</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7107799</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122507137</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Myrsnipmyrarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>509318</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7107804</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122507138</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Myrsnipmyrarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>509236</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7107905</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122507139</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Myrsnipmyrarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>509228</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7107904</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60503-2023 artfynd.xlsx
+++ b/artfynd/A 60503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557466</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557422</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557424</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557425</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557426</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557427</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557428</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557429</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557430</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557431</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557432</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557433</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557434</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557435</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557436</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557437</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557438</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557439</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557440</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557441</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557442</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557444</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557445</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557446</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,6 +3454,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557447</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557448</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3528,6 +3668,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557449</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,6 +3775,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557450</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3732,6 +3882,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557451</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3834,6 +3989,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557453</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557454</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4038,6 +4203,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557455</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4140,6 +4310,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557456</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4242,6 +4417,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557457</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4344,6 +4524,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557458</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4446,6 +4631,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507135</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4548,6 +4738,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507136</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4650,6 +4845,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507137</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4752,6 +4952,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507138</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4854,8 +5059,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507139</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>